--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/198.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/198.xlsx
@@ -426,13 +426,13 @@
         <v>-15.46462005568967</v>
       </c>
       <c r="E2">
-        <v>-13.08404051453743</v>
+        <v>-10.10766927367803</v>
       </c>
       <c r="F2">
-        <v>1.138602347316988</v>
+        <v>0.6971649115651429</v>
       </c>
       <c r="G2">
-        <v>-6.445166528708298</v>
+        <v>-5.405062641725616</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.17897851912585</v>
       </c>
       <c r="E3">
-        <v>-11.97478627788457</v>
+        <v>-12.27097564883025</v>
       </c>
       <c r="F3">
-        <v>0.786677553611696</v>
+        <v>0.4875147143322266</v>
       </c>
       <c r="G3">
-        <v>-6.760628413145449</v>
+        <v>-3.476375226547154</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.80464378534764</v>
       </c>
       <c r="E4">
-        <v>-13.74866653074718</v>
+        <v>-14.09859077426788</v>
       </c>
       <c r="F4">
-        <v>1.225775855726437</v>
+        <v>0.4980360645814486</v>
       </c>
       <c r="G4">
-        <v>-6.396335982004048</v>
+        <v>-4.558023149502151</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.3570266888273</v>
       </c>
       <c r="E5">
-        <v>-14.46181514594911</v>
+        <v>-14.45993130076192</v>
       </c>
       <c r="F5">
-        <v>1.150969506810655</v>
+        <v>0.7449516538576129</v>
       </c>
       <c r="G5">
-        <v>-7.009945597707962</v>
+        <v>-4.623472634813542</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.81975129525439</v>
       </c>
       <c r="E6">
-        <v>-15.3581903479754</v>
+        <v>-12.88853270620428</v>
       </c>
       <c r="F6">
-        <v>1.516726387981395</v>
+        <v>0.1405754268487378</v>
       </c>
       <c r="G6">
-        <v>-7.259732879737052</v>
+        <v>-4.630434712082629</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.18975440800393</v>
       </c>
       <c r="E7">
-        <v>-14.0382035733756</v>
+        <v>-15.36829790196052</v>
       </c>
       <c r="F7">
-        <v>1.345610131229994</v>
+        <v>0.09235870840022604</v>
       </c>
       <c r="G7">
-        <v>-6.37906486592567</v>
+        <v>-2.859531207851372</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.45788930658868</v>
       </c>
       <c r="E8">
-        <v>-14.89586937958432</v>
+        <v>-14.43490695339553</v>
       </c>
       <c r="F8">
-        <v>1.38905751931416</v>
+        <v>0.6059086093056911</v>
       </c>
       <c r="G8">
-        <v>-7.81827488094073</v>
+        <v>-5.683290820482584</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.62703002480632</v>
       </c>
       <c r="E9">
-        <v>-17.52436777564848</v>
+        <v>-13.53032615646735</v>
       </c>
       <c r="F9">
-        <v>1.397601612727955</v>
+        <v>1.189244511374995</v>
       </c>
       <c r="G9">
-        <v>-6.365590945580836</v>
+        <v>-5.207039049748571</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.70774645425523</v>
       </c>
       <c r="E10">
-        <v>-17.01595599880733</v>
+        <v>-16.94490877010099</v>
       </c>
       <c r="F10">
-        <v>1.927848525099899</v>
+        <v>0.8169532595971518</v>
       </c>
       <c r="G10">
-        <v>-6.024634549945757</v>
+        <v>-3.912549532982751</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.712161507168256</v>
       </c>
       <c r="E11">
-        <v>-16.58917449442844</v>
+        <v>-17.01842854561552</v>
       </c>
       <c r="F11">
-        <v>1.68073655629022</v>
+        <v>1.178499066738739</v>
       </c>
       <c r="G11">
-        <v>-4.87849057879468</v>
+        <v>-2.885995708892306</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.660074488196791</v>
       </c>
       <c r="E12">
-        <v>-17.15825876602436</v>
+        <v>-18.47950898487231</v>
       </c>
       <c r="F12">
-        <v>1.363593111899809</v>
+        <v>1.747237951385438</v>
       </c>
       <c r="G12">
-        <v>-4.6093995057261</v>
+        <v>-4.141112907559573</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.572843774561231</v>
       </c>
       <c r="E13">
-        <v>-18.43064222185554</v>
+        <v>-19.59855831080376</v>
       </c>
       <c r="F13">
-        <v>1.776783568943876</v>
+        <v>1.217771806029806</v>
       </c>
       <c r="G13">
-        <v>-4.800520610253765</v>
+        <v>-4.506597135095112</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.494808203605253</v>
       </c>
       <c r="E14">
-        <v>-19.50580157770464</v>
+        <v>-19.60773752761731</v>
       </c>
       <c r="F14">
-        <v>1.750630249456309</v>
+        <v>1.373345572927085</v>
       </c>
       <c r="G14">
-        <v>-3.425879475436651</v>
+        <v>-2.319965253678796</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.459931900497193</v>
       </c>
       <c r="E15">
-        <v>-20.46066202154</v>
+        <v>-20.38776264696452</v>
       </c>
       <c r="F15">
-        <v>2.216299969420293</v>
+        <v>1.725271950338293</v>
       </c>
       <c r="G15">
-        <v>-3.542016723499823</v>
+        <v>-0.7317542050322193</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.503076829280057</v>
       </c>
       <c r="E16">
-        <v>-22.13233008757548</v>
+        <v>-20.71697365037414</v>
       </c>
       <c r="F16">
-        <v>2.188157515302934</v>
+        <v>2.09127272222001</v>
       </c>
       <c r="G16">
-        <v>-2.89092511120028</v>
+        <v>-1.292491097928434</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.651494398306194</v>
       </c>
       <c r="E17">
-        <v>-21.89768267839403</v>
+        <v>-22.34111085322511</v>
       </c>
       <c r="F17">
-        <v>2.478403298425522</v>
+        <v>1.777684697609761</v>
       </c>
       <c r="G17">
-        <v>-1.506200054670546</v>
+        <v>-1.502525349121955</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.935499389579205</v>
       </c>
       <c r="E18">
-        <v>-22.15500868540589</v>
+        <v>-22.02676230150866</v>
       </c>
       <c r="F18">
-        <v>2.737980616495624</v>
+        <v>2.229294276456474</v>
       </c>
       <c r="G18">
-        <v>-0.5823161793895179</v>
+        <v>-1.292858568483293</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.373574764901968</v>
       </c>
       <c r="E19">
-        <v>-23.38938013041668</v>
+        <v>-22.75404428408854</v>
       </c>
       <c r="F19">
-        <v>2.61681919543493</v>
+        <v>2.193016325051503</v>
       </c>
       <c r="G19">
-        <v>-0.4723464776660076</v>
+        <v>-0.6543205448686662</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.973058779732055</v>
       </c>
       <c r="E20">
-        <v>-24.8576246155536</v>
+        <v>-23.94287286600419</v>
       </c>
       <c r="F20">
-        <v>3.038503067303498</v>
+        <v>3.027489976367533</v>
       </c>
       <c r="G20">
-        <v>0.2761115894890402</v>
+        <v>0.6800312507355177</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.733873020029714</v>
       </c>
       <c r="E21">
-        <v>-24.84548830521304</v>
+        <v>-23.03353264289394</v>
       </c>
       <c r="F21">
-        <v>2.962927037312812</v>
+        <v>2.808914804448157</v>
       </c>
       <c r="G21">
-        <v>0.8021870705890852</v>
+        <v>1.769770146988493</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.649400471415995</v>
       </c>
       <c r="E22">
-        <v>-26.7404871238848</v>
+        <v>-25.01578609874549</v>
       </c>
       <c r="F22">
-        <v>2.759737568361932</v>
+        <v>3.052298729532891</v>
       </c>
       <c r="G22">
-        <v>1.203322563037036</v>
+        <v>0.6505144267073758</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.712420594243086</v>
       </c>
       <c r="E23">
-        <v>-25.24127693348343</v>
+        <v>-24.85374824180303</v>
       </c>
       <c r="F23">
-        <v>3.194091087554016</v>
+        <v>3.407961069198621</v>
       </c>
       <c r="G23">
-        <v>0.5344963582836171</v>
+        <v>1.354071564713288</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.903163005549326</v>
       </c>
       <c r="E24">
-        <v>-26.75044523822767</v>
+        <v>-27.2824594215968</v>
       </c>
       <c r="F24">
-        <v>3.494192272588383</v>
+        <v>3.211242622618225</v>
       </c>
       <c r="G24">
-        <v>0.5037744956791804</v>
+        <v>2.436523950234328</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.204063605653562</v>
       </c>
       <c r="E25">
-        <v>-27.02454471296394</v>
+        <v>-27.65013075475356</v>
       </c>
       <c r="F25">
-        <v>3.312566543382126</v>
+        <v>3.765386073548235</v>
       </c>
       <c r="G25">
-        <v>0.2510143437558253</v>
+        <v>0.3411571882446405</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.592227496980023</v>
       </c>
       <c r="E26">
-        <v>-27.54991562496382</v>
+        <v>-27.95298603943854</v>
       </c>
       <c r="F26">
-        <v>3.369025659267542</v>
+        <v>3.029753092120695</v>
       </c>
       <c r="G26">
-        <v>0.901457089129671</v>
+        <v>1.126166988698782</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.047824332835559</v>
       </c>
       <c r="E27">
-        <v>-28.16093356587076</v>
+        <v>-24.66979709913745</v>
       </c>
       <c r="F27">
-        <v>3.574606524150737</v>
+        <v>3.672492219372218</v>
       </c>
       <c r="G27">
-        <v>1.15524682071574</v>
+        <v>1.330073420099112</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.543014304060824</v>
       </c>
       <c r="E28">
-        <v>-27.7813387606518</v>
+        <v>-27.4228557012566</v>
       </c>
       <c r="F28">
-        <v>3.339098368583483</v>
+        <v>3.500680715723939</v>
       </c>
       <c r="G28">
-        <v>0.970319746892051</v>
+        <v>2.020150016669112</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.056183309962223</v>
       </c>
       <c r="E29">
-        <v>-28.11521409228932</v>
+        <v>-24.70704379785054</v>
       </c>
       <c r="F29">
-        <v>3.416939098033247</v>
+        <v>2.610348173064444</v>
       </c>
       <c r="G29">
-        <v>0.3533731012845511</v>
+        <v>1.762784895900631</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.566592642660895</v>
       </c>
       <c r="E30">
-        <v>-27.18925889804493</v>
+        <v>-27.54243005742914</v>
       </c>
       <c r="F30">
-        <v>3.11660510822931</v>
+        <v>3.321745702868013</v>
       </c>
       <c r="G30">
-        <v>-0.06476204250755688</v>
+        <v>1.433064491825838</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.056127426819801</v>
       </c>
       <c r="E31">
-        <v>-27.4566834020939</v>
+        <v>-27.71398676673572</v>
       </c>
       <c r="F31">
-        <v>3.630503424436172</v>
+        <v>3.240701136351314</v>
       </c>
       <c r="G31">
-        <v>0.226046209298642</v>
+        <v>0.8271883105016612</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.507127747119247</v>
       </c>
       <c r="E32">
-        <v>-27.22156050314165</v>
+        <v>-23.78822095016823</v>
       </c>
       <c r="F32">
-        <v>2.7908146295406</v>
+        <v>3.570283007001587</v>
       </c>
       <c r="G32">
-        <v>-1.116936178526422</v>
+        <v>1.278001849311915</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.904679019929845</v>
       </c>
       <c r="E33">
-        <v>-27.38773285685311</v>
+        <v>-25.31409479552677</v>
       </c>
       <c r="F33">
-        <v>3.247854735971354</v>
+        <v>3.258300860189593</v>
       </c>
       <c r="G33">
-        <v>-0.1867225401743074</v>
+        <v>-0.3404179273805115</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.241137815226839</v>
       </c>
       <c r="E34">
-        <v>-27.50096734941491</v>
+        <v>-25.52489526058383</v>
       </c>
       <c r="F34">
-        <v>3.857112736464572</v>
+        <v>3.526427022791238</v>
       </c>
       <c r="G34">
-        <v>0.3795628270457255</v>
+        <v>-0.3241399749639151</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.510067450040887</v>
       </c>
       <c r="E35">
-        <v>-26.75139168929527</v>
+        <v>-26.88168494344396</v>
       </c>
       <c r="F35">
-        <v>3.709641209030681</v>
+        <v>3.070067909904122</v>
       </c>
       <c r="G35">
-        <v>-0.8686287103533865</v>
+        <v>-0.910152883052465</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.710420430215463</v>
       </c>
       <c r="E36">
-        <v>-26.3552000268382</v>
+        <v>-25.800706498495</v>
       </c>
       <c r="F36">
-        <v>3.569328032334577</v>
+        <v>3.233173782135231</v>
       </c>
       <c r="G36">
-        <v>-0.8682281343431347</v>
+        <v>-0.4096513662432898</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.839990213886974</v>
       </c>
       <c r="E37">
-        <v>-24.65575430123967</v>
+        <v>-23.7845393008</v>
       </c>
       <c r="F37">
-        <v>3.754279543963257</v>
+        <v>2.987618596240429</v>
       </c>
       <c r="G37">
-        <v>-0.4272038786925057</v>
+        <v>-0.03671841124439065</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.907160027147325</v>
       </c>
       <c r="E38">
-        <v>-23.94799457010686</v>
+        <v>-25.87207524885588</v>
       </c>
       <c r="F38">
-        <v>3.739809223013887</v>
+        <v>3.609042625576052</v>
       </c>
       <c r="G38">
-        <v>-0.9047600043689923</v>
+        <v>0.7559387494054668</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.9200676603969</v>
       </c>
       <c r="E39">
-        <v>-23.35813818823776</v>
+        <v>-21.47729085083997</v>
       </c>
       <c r="F39">
-        <v>3.888273734056758</v>
+        <v>3.968776673150376</v>
       </c>
       <c r="G39">
-        <v>-1.448484003738892</v>
+        <v>0.09519689685894835</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.891727157874072</v>
       </c>
       <c r="E40">
-        <v>-22.52821834227403</v>
+        <v>-22.4836808004086</v>
       </c>
       <c r="F40">
-        <v>4.000770700054084</v>
+        <v>3.698461828973594</v>
       </c>
       <c r="G40">
-        <v>-1.750528247105377</v>
+        <v>-0.5742682431835496</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.832747138259894</v>
       </c>
       <c r="E41">
-        <v>-22.65067733638946</v>
+        <v>-20.61324442475444</v>
       </c>
       <c r="F41">
-        <v>4.013240800432254</v>
+        <v>3.64136289589834</v>
       </c>
       <c r="G41">
-        <v>-1.612955216675424</v>
+        <v>-1.910560018473747</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.755720844748422</v>
       </c>
       <c r="E42">
-        <v>-22.72056980422384</v>
+        <v>-19.44217651789688</v>
       </c>
       <c r="F42">
-        <v>4.012976321544376</v>
+        <v>3.774913648335518</v>
       </c>
       <c r="G42">
-        <v>-0.9731227697549423</v>
+        <v>0.4637698633826274</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.672355496533302</v>
       </c>
       <c r="E43">
-        <v>-21.46111967015858</v>
+        <v>-21.16937726068842</v>
       </c>
       <c r="F43">
-        <v>4.275629196502262</v>
+        <v>4.119790950717105</v>
       </c>
       <c r="G43">
-        <v>-1.525570056620822</v>
+        <v>-0.9496741757002845</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.591857917269394</v>
       </c>
       <c r="E44">
-        <v>-19.83090978366332</v>
+        <v>-20.31494478492118</v>
       </c>
       <c r="F44">
-        <v>4.438177604251136</v>
+        <v>4.07059946127764</v>
       </c>
       <c r="G44">
-        <v>-1.41079013222875</v>
+        <v>-2.207098824608424</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.523186706331975</v>
       </c>
       <c r="E45">
-        <v>-18.633418230971</v>
+        <v>-18.25023687433796</v>
       </c>
       <c r="F45">
-        <v>4.598350453126851</v>
+        <v>3.743633872799673</v>
       </c>
       <c r="G45">
-        <v>-1.78222009955282</v>
+        <v>-0.9960019499768454</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.467411624855485</v>
       </c>
       <c r="E46">
-        <v>-17.86370897541326</v>
+        <v>-17.28349371470649</v>
       </c>
       <c r="F46">
-        <v>4.839716736875315</v>
+        <v>4.58031045904408</v>
       </c>
       <c r="G46">
-        <v>-2.78327279135426</v>
+        <v>-2.039158159946736</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.427552604955691</v>
       </c>
       <c r="E47">
-        <v>-17.91554641737906</v>
+        <v>-19.16391537554756</v>
       </c>
       <c r="F47">
-        <v>4.537616914975663</v>
+        <v>3.496317605926903</v>
       </c>
       <c r="G47">
-        <v>-2.325589870550018</v>
+        <v>-1.642945448715682</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.399815992885319</v>
       </c>
       <c r="E48">
-        <v>-16.90502649951544</v>
+        <v>-16.08319903660342</v>
       </c>
       <c r="F48">
-        <v>4.896953452365212</v>
+        <v>4.131084357600104</v>
       </c>
       <c r="G48">
-        <v>-2.801014004899214</v>
+        <v>-2.389979981288843</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.385451047766922</v>
       </c>
       <c r="E49">
-        <v>-16.67342675334115</v>
+        <v>-15.9335239137019</v>
       </c>
       <c r="F49">
-        <v>4.20687893900712</v>
+        <v>4.118151815094625</v>
       </c>
       <c r="G49">
-        <v>-2.274604158699703</v>
+        <v>-1.289680444765593</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.376702447913321</v>
       </c>
       <c r="E50">
-        <v>-15.56106598351903</v>
+        <v>-14.360205246165</v>
       </c>
       <c r="F50">
-        <v>4.749293463927384</v>
+        <v>4.162441734725805</v>
       </c>
       <c r="G50">
-        <v>-2.566210251980866</v>
+        <v>-1.362674663360983</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.3704508732613</v>
       </c>
       <c r="E51">
-        <v>-15.55256603780663</v>
+        <v>-15.86979922746596</v>
       </c>
       <c r="F51">
-        <v>4.411683787991749</v>
+        <v>4.236644691687804</v>
       </c>
       <c r="G51">
-        <v>-2.505587542065732</v>
+        <v>-1.470065450109401</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.361522888237972</v>
       </c>
       <c r="E52">
-        <v>-14.37165322845639</v>
+        <v>-14.44484242536836</v>
       </c>
       <c r="F52">
-        <v>4.989731696009401</v>
+        <v>4.808837638936077</v>
       </c>
       <c r="G52">
-        <v>-3.372102973696729</v>
+        <v>-1.019791530222048</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.349421399289527</v>
       </c>
       <c r="E53">
-        <v>-14.95734341423844</v>
+        <v>-13.08665344403985</v>
       </c>
       <c r="F53">
-        <v>4.91514706592178</v>
+        <v>5.106200596442649</v>
       </c>
       <c r="G53">
-        <v>-2.781905536046541</v>
+        <v>-0.4032057340783289</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.3339834955672</v>
       </c>
       <c r="E54">
-        <v>-13.55351194338662</v>
+        <v>-11.8421472741999</v>
       </c>
       <c r="F54">
-        <v>4.787718920553692</v>
+        <v>4.932974843411882</v>
       </c>
       <c r="G54">
-        <v>-2.988602757336476</v>
+        <v>-1.691521083413408</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.314468541764639</v>
       </c>
       <c r="E55">
-        <v>-12.24457011689153</v>
+        <v>-14.27895989399339</v>
       </c>
       <c r="F55">
-        <v>4.971238762034815</v>
+        <v>4.19158192356989</v>
       </c>
       <c r="G55">
-        <v>-3.43028912209496</v>
+        <v>-0.608747574975059</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.293214891756444</v>
       </c>
       <c r="E56">
-        <v>-10.77196471128522</v>
+        <v>-11.85078760260654</v>
       </c>
       <c r="F56">
-        <v>4.941737488242008</v>
+        <v>4.921817635237612</v>
       </c>
       <c r="G56">
-        <v>-2.908590182197831</v>
+        <v>-0.580743670258364</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.270084509366082</v>
       </c>
       <c r="E57">
-        <v>-10.98465807847748</v>
+        <v>-11.54349441339404</v>
       </c>
       <c r="F57">
-        <v>4.470908054405523</v>
+        <v>4.356217655715313</v>
       </c>
       <c r="G57">
-        <v>-3.128791118742454</v>
+        <v>-1.664013760527603</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.250207581089433</v>
       </c>
       <c r="E58">
-        <v>-9.879243987783124</v>
+        <v>-10.4368485777696</v>
       </c>
       <c r="F58">
-        <v>4.590675814260631</v>
+        <v>4.695797461809756</v>
       </c>
       <c r="G58">
-        <v>-3.341864450741026</v>
+        <v>-1.781279904619667</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.230176743870715</v>
       </c>
       <c r="E59">
-        <v>-10.84503163939898</v>
+        <v>-11.75349786702575</v>
       </c>
       <c r="F59">
-        <v>4.696554473237335</v>
+        <v>4.715820255698656</v>
       </c>
       <c r="G59">
-        <v>-4.829328977536503</v>
+        <v>-1.263758873193099</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.211250175859767</v>
       </c>
       <c r="E60">
-        <v>-11.19073534514454</v>
+        <v>-11.57177473357194</v>
       </c>
       <c r="F60">
-        <v>4.362094788367509</v>
+        <v>4.287757216402697</v>
       </c>
       <c r="G60">
-        <v>-2.971334951803638</v>
+        <v>-2.180832956299846</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.189582664569403</v>
       </c>
       <c r="E61">
-        <v>-10.83345685983537</v>
+        <v>-9.728260135893386</v>
       </c>
       <c r="F61">
-        <v>4.657199381238665</v>
+        <v>4.40092884112</v>
       </c>
       <c r="G61">
-        <v>-4.080457092189046</v>
+        <v>-2.869595266290756</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.165042196630883</v>
       </c>
       <c r="E62">
-        <v>-11.06448601828469</v>
+        <v>-9.30107106885381</v>
       </c>
       <c r="F62">
-        <v>4.832849788025969</v>
+        <v>4.887593750404965</v>
       </c>
       <c r="G62">
-        <v>-3.866092647430158</v>
+        <v>-2.234765053680113</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.132374387325892</v>
       </c>
       <c r="E63">
-        <v>-9.30377456783639</v>
+        <v>-8.847404014291387</v>
       </c>
       <c r="F63">
-        <v>4.55540826722971</v>
+        <v>4.359598867844777</v>
       </c>
       <c r="G63">
-        <v>-3.505931777121767</v>
+        <v>-3.136190188022725</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.087684461527417</v>
       </c>
       <c r="E64">
-        <v>-9.227800359409704</v>
+        <v>-6.529912156126004</v>
       </c>
       <c r="F64">
-        <v>3.876850463288693</v>
+        <v>3.88431763667999</v>
       </c>
       <c r="G64">
-        <v>-3.865069688858523</v>
+        <v>-1.598567585761751</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.026792191751958</v>
       </c>
       <c r="E65">
-        <v>-7.645492670967582</v>
+        <v>-8.588157934300273</v>
       </c>
       <c r="F65">
-        <v>4.086623397730056</v>
+        <v>4.362736189263262</v>
       </c>
       <c r="G65">
-        <v>-3.495410863397963</v>
+        <v>-3.004821119933366</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.946895370495015</v>
       </c>
       <c r="E66">
-        <v>-8.011461297897462</v>
+        <v>-8.484157000240117</v>
       </c>
       <c r="F66">
-        <v>3.793275134719123</v>
+        <v>3.623634891880911</v>
       </c>
       <c r="G66">
-        <v>-3.361893251253617</v>
+        <v>-2.590562624967744</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.84811680638891</v>
       </c>
       <c r="E67">
-        <v>-7.733639417526885</v>
+        <v>-7.069103970797291</v>
       </c>
       <c r="F67">
-        <v>3.715974448986524</v>
+        <v>3.282642420109898</v>
       </c>
       <c r="G67">
-        <v>-4.041591287558003</v>
+        <v>-3.085810306006096</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.72777466054092</v>
       </c>
       <c r="E68">
-        <v>-6.921290050712923</v>
+        <v>-6.901917238908108</v>
       </c>
       <c r="F68">
-        <v>3.313467672048011</v>
+        <v>2.936425302523849</v>
       </c>
       <c r="G68">
-        <v>-4.060461397131848</v>
+        <v>-3.289547899583924</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.587283628016662</v>
       </c>
       <c r="E69">
-        <v>-8.086806048437081</v>
+        <v>-7.29941310187939</v>
       </c>
       <c r="F69">
-        <v>3.572012413861247</v>
+        <v>3.042182016145064</v>
       </c>
       <c r="G69">
-        <v>-3.865920499062116</v>
+        <v>-2.397051306560726</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.42567272148232</v>
       </c>
       <c r="E70">
-        <v>-7.750412885251296</v>
+        <v>-5.914488010009595</v>
       </c>
       <c r="F70">
-        <v>3.288137879636472</v>
+        <v>2.921315164384641</v>
       </c>
       <c r="G70">
-        <v>-3.360188320300892</v>
+        <v>-1.73657098711181</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.249545105426977</v>
       </c>
       <c r="E71">
-        <v>-7.812027302599659</v>
+        <v>-7.557373095252324</v>
       </c>
       <c r="F71">
-        <v>2.661403684366381</v>
+        <v>2.988982167033623</v>
       </c>
       <c r="G71">
-        <v>-4.292490912888287</v>
+        <v>-2.880639246209765</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.059803481482964</v>
       </c>
       <c r="E72">
-        <v>-7.948329841756529</v>
+        <v>-6.916852146185406</v>
       </c>
       <c r="F72">
-        <v>2.510085335263888</v>
+        <v>2.752290983147535</v>
       </c>
       <c r="G72">
-        <v>-3.485528884963239</v>
+        <v>-5.234341118810939</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.861334339154344</v>
       </c>
       <c r="E73">
-        <v>-7.174006071184975</v>
+        <v>-7.724451143765322</v>
       </c>
       <c r="F73">
-        <v>2.157300589246512</v>
+        <v>2.418735594355425</v>
       </c>
       <c r="G73">
-        <v>-2.974969930805758</v>
+        <v>-1.972695647700327</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.657170079905674</v>
       </c>
       <c r="E74">
-        <v>-8.946505139475244</v>
+        <v>-8.541120674782603</v>
       </c>
       <c r="F74">
-        <v>2.848501117510482</v>
+        <v>2.872826840371632</v>
       </c>
       <c r="G74">
-        <v>-2.984332153590817</v>
+        <v>-0.5875335991594093</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.454343944814712</v>
       </c>
       <c r="E75">
-        <v>-7.601448732768979</v>
+        <v>-8.286140417306715</v>
       </c>
       <c r="F75">
-        <v>2.360702274790062</v>
+        <v>1.931687428238924</v>
       </c>
       <c r="G75">
-        <v>-3.08393322668533</v>
+        <v>-1.325182735128737</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.25895763983201</v>
       </c>
       <c r="E76">
-        <v>-7.727865613167105</v>
+        <v>-7.198233407126011</v>
       </c>
       <c r="F76">
-        <v>2.09602700737816</v>
+        <v>2.353094151572291</v>
       </c>
       <c r="G76">
-        <v>-1.64027052791995</v>
+        <v>-2.872902501284488</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.075729091790346</v>
       </c>
       <c r="E77">
-        <v>-9.420735994506499</v>
+        <v>-8.60873079171712</v>
       </c>
       <c r="F77">
-        <v>2.075139510059429</v>
+        <v>2.658749393252104</v>
       </c>
       <c r="G77">
-        <v>-2.449334752262436</v>
+        <v>-0.9377760750321438</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.910533353482168</v>
       </c>
       <c r="E78">
-        <v>-9.513818777734164</v>
+        <v>-11.49856742276394</v>
       </c>
       <c r="F78">
-        <v>2.102014999444436</v>
+        <v>1.540686274776079</v>
       </c>
       <c r="G78">
-        <v>-1.73525338998718</v>
+        <v>-0.4855191383667677</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.767751001011985</v>
       </c>
       <c r="E79">
-        <v>-7.951155609537316</v>
+        <v>-10.9637682278801</v>
       </c>
       <c r="F79">
-        <v>1.687977259735609</v>
+        <v>2.432307954050741</v>
       </c>
       <c r="G79">
-        <v>-1.327354453002499</v>
+        <v>0.1462024719824995</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.655867371680005</v>
       </c>
       <c r="E80">
-        <v>-9.449093298742531</v>
+        <v>-10.4862678146153</v>
       </c>
       <c r="F80">
-        <v>2.448803834865958</v>
+        <v>1.208980654493202</v>
       </c>
       <c r="G80">
-        <v>-1.089703630920377</v>
+        <v>-1.322388634693592</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.576657017530299</v>
       </c>
       <c r="E81">
-        <v>-11.69001771838622</v>
+        <v>-11.08425733580218</v>
       </c>
       <c r="F81">
-        <v>1.29274444406671</v>
+        <v>1.869658418648907</v>
       </c>
       <c r="G81">
-        <v>-1.025402904911113</v>
+        <v>-0.06642724691381029</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.536973686286524</v>
       </c>
       <c r="E82">
-        <v>-11.12381355625918</v>
+        <v>-10.81698227139547</v>
       </c>
       <c r="F82">
-        <v>1.941056632434664</v>
+        <v>1.345028911159027</v>
       </c>
       <c r="G82">
-        <v>-0.2678772535240013</v>
+        <v>1.139362823218316</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.541254810872822</v>
       </c>
       <c r="E83">
-        <v>-12.06580860543874</v>
+        <v>-11.62829461766168</v>
       </c>
       <c r="F83">
-        <v>1.453935615846052</v>
+        <v>1.773262990693854</v>
       </c>
       <c r="G83">
-        <v>0.03381607201532126</v>
+        <v>0.5266139493546124</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.598469503827218</v>
       </c>
       <c r="E84">
-        <v>-14.01823753147578</v>
+        <v>-11.43271888221841</v>
       </c>
       <c r="F84">
-        <v>1.863051197569694</v>
+        <v>0.886259397868613</v>
       </c>
       <c r="G84">
-        <v>0.4518055518037014</v>
+        <v>1.07702525071384</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.710919238910754</v>
       </c>
       <c r="E85">
-        <v>-14.95159678072271</v>
+        <v>-14.39800894718103</v>
       </c>
       <c r="F85">
-        <v>1.72818280181087</v>
+        <v>1.512876398900962</v>
       </c>
       <c r="G85">
-        <v>0.2991231915325142</v>
+        <v>-0.221814322890582</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.884037300585065</v>
       </c>
       <c r="E86">
-        <v>-15.17081115048601</v>
+        <v>-16.85764054749918</v>
       </c>
       <c r="F86">
-        <v>1.410420128407522</v>
+        <v>0.8412156342216842</v>
       </c>
       <c r="G86">
-        <v>0.7211680896065015</v>
+        <v>0.7572563465300967</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.12223755953656</v>
       </c>
       <c r="E87">
-        <v>-15.09455617667085</v>
+        <v>-17.61907175257089</v>
       </c>
       <c r="F87">
-        <v>0.9356884431953936</v>
+        <v>1.253522383364936</v>
       </c>
       <c r="G87">
-        <v>-0.05838593179892057</v>
+        <v>2.393546448043509</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.428729349669432</v>
       </c>
       <c r="E88">
-        <v>-17.46404850186631</v>
+        <v>-19.14608677337936</v>
       </c>
       <c r="F88">
-        <v>1.653640931782966</v>
+        <v>0.5638643846626047</v>
       </c>
       <c r="G88">
-        <v>0.6651304852632581</v>
+        <v>2.625261461973718</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.802936279308962</v>
       </c>
       <c r="E89">
-        <v>-19.2181981934775</v>
+        <v>-20.68997941681441</v>
       </c>
       <c r="F89">
-        <v>0.8296482462153145</v>
+        <v>1.164274220206262</v>
       </c>
       <c r="G89">
-        <v>1.057595658943857</v>
+        <v>2.589563849423756</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.237982226858424</v>
       </c>
       <c r="E90">
-        <v>-21.07750810849481</v>
+        <v>-20.58562979025567</v>
       </c>
       <c r="F90">
-        <v>0.8140614125955594</v>
+        <v>0.5385908138110642</v>
       </c>
       <c r="G90">
-        <v>0.6218517234283658</v>
+        <v>1.7998994219414</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.731226419293489</v>
       </c>
       <c r="E91">
-        <v>-21.16425555658575</v>
+        <v>-23.95139092561261</v>
       </c>
       <c r="F91">
-        <v>0.7433505271771036</v>
+        <v>0.3942146395889002</v>
       </c>
       <c r="G91">
-        <v>0.002561211579061985</v>
+        <v>0.9353272805419546</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.273486857250438</v>
       </c>
       <c r="E92">
-        <v>-22.29094894664215</v>
+        <v>-24.9692062151026</v>
       </c>
       <c r="F92">
-        <v>0.809562104089796</v>
+        <v>-0.5767902986971647</v>
       </c>
       <c r="G92">
-        <v>0.386001838119608</v>
+        <v>2.686589318088716</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.856541554925495</v>
       </c>
       <c r="E93">
-        <v>-24.95004624157614</v>
+        <v>-25.90098049844684</v>
       </c>
       <c r="F93">
-        <v>0.1987172302693085</v>
+        <v>0.2264938483202009</v>
       </c>
       <c r="G93">
-        <v>0.2860200522880788</v>
+        <v>2.345334973355103</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.458833318460526</v>
       </c>
       <c r="E94">
-        <v>-26.52810169292506</v>
+        <v>-28.54380698627128</v>
       </c>
       <c r="F94">
-        <v>0.2649786939183372</v>
+        <v>0.1506406697943131</v>
       </c>
       <c r="G94">
-        <v>0.005100400007682986</v>
+        <v>1.398571917852172</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.069443195752029</v>
       </c>
       <c r="E95">
-        <v>-27.3844768840416</v>
+        <v>-28.55954796192194</v>
       </c>
       <c r="F95">
-        <v>-0.1311425807691237</v>
+        <v>-0.3614791446695101</v>
       </c>
       <c r="G95">
-        <v>0.08301408927443037</v>
+        <v>0.4835437518886942</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.673717091788744</v>
       </c>
       <c r="E96">
-        <v>-32.04606764940443</v>
+        <v>-33.50710506815814</v>
       </c>
       <c r="F96">
-        <v>-0.06083395665318943</v>
+        <v>0.3402791590797366</v>
       </c>
       <c r="G96">
-        <v>0.8235831264093949</v>
+        <v>0.413396602457077</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.255021024596072</v>
       </c>
       <c r="E97">
-        <v>-32.95314137127384</v>
+        <v>-32.93081373017902</v>
       </c>
       <c r="F97">
-        <v>-0.3922822247248073</v>
+        <v>-0.3118568872210459</v>
       </c>
       <c r="G97">
-        <v>0.2491902331636869</v>
+        <v>-0.6558235325434953</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.800489529996419</v>
       </c>
       <c r="E98">
-        <v>-35.08922482492895</v>
+        <v>-37.58064404854392</v>
       </c>
       <c r="F98">
-        <v>-0.7031383566309238</v>
+        <v>-1.093953424648705</v>
       </c>
       <c r="G98">
-        <v>0.1096474281378671</v>
+        <v>1.224837798496759</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.28938488276798</v>
       </c>
       <c r="E99">
-        <v>-37.85897991071437</v>
+        <v>-37.73145581842137</v>
       </c>
       <c r="F99">
-        <v>-1.246115097151169</v>
+        <v>-1.561650288184452</v>
       </c>
       <c r="G99">
-        <v>-0.6102638048320452</v>
+        <v>-0.7474528119794432</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.72691917452542</v>
       </c>
       <c r="E100">
-        <v>-39.10017576605472</v>
+        <v>-41.33158359757129</v>
       </c>
       <c r="F100">
-        <v>-0.711746590134295</v>
+        <v>-1.699513471829371</v>
       </c>
       <c r="G100">
-        <v>-0.2745645555133291</v>
+        <v>-1.208078807768097</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.08826688605472</v>
       </c>
       <c r="E101">
-        <v>-40.89634743222009</v>
+        <v>-42.36547723402551</v>
       </c>
       <c r="F101">
-        <v>-0.9028824733627664</v>
+        <v>-1.669601226351508</v>
       </c>
       <c r="G101">
-        <v>-1.095030298693064</v>
+        <v>-0.2524964589485473</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.40533693570318</v>
       </c>
       <c r="E102">
-        <v>-43.43785837107092</v>
+        <v>-42.3239103711091</v>
       </c>
       <c r="F102">
-        <v>-1.180339039365223</v>
+        <v>-1.725432402841453</v>
       </c>
       <c r="G102">
-        <v>-1.300575450135334</v>
+        <v>-1.858557969142875</v>
       </c>
     </row>
   </sheetData>
